--- a/Configs/GameConfig/Datas/enemy.xlsx
+++ b/Configs/GameConfig/Datas/enemy.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>(list#sep=,),float?</t>
+          <t>(list#sep=,),float</t>
         </is>
       </c>
     </row>
@@ -496,12 +496,6 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -541,7 +535,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>Mob0</t>
@@ -557,12 +550,8 @@
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>Mob1</t>
@@ -573,17 +562,13 @@
           <t>pm</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>resources/img/gameObject/enemy/mob_1.png</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>Mob2</t>
@@ -594,17 +579,13 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>resources/img/gameObject/enemy/mob_2.png</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>Mob3</t>
@@ -615,17 +596,13 @@
           <t>q6</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>resources/img/gameObject/enemy/mob_3.png</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>Zombie</t>
@@ -636,7 +613,6 @@
           <t>sQ</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>resources/img/gameObject/enemy/zombie.png</t>
@@ -647,10 +623,8 @@
           <t>bubble VFX</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>Cavalry</t>
@@ -661,7 +635,6 @@
           <t>qT</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>resources/img/gameObject/soldier/soldier_3.png</t>
@@ -672,10 +645,8 @@
           <t>yellow-circle VFX</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>Puppet</t>
@@ -686,13 +657,11 @@
           <t>oo</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>resources/img/gameObject/soldier/soldier_{skin}.png</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>1,1.2,1.4,1.6,1.8</t>

--- a/Configs/GameConfig/Datas/enemy.xlsx
+++ b/Configs/GameConfig/Datas/enemy.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,16 @@
           <t>levelMultipliers</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>typeIndex</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>resourceAddress</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,180 +499,249 @@
           <t>(list#sep=,),float</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int?</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string?</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##group</t>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>类型索引</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>资源地址</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>键(主键)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>符号</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>资源路径</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>延迟项</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>等级倍数</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Mob0</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>st</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mob1</t>
+          <t>Mob0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pm</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>resources/img/gameObject/enemy/mob_1.png</t>
+          <t>st</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Mob0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mob2</t>
+          <t>Mob1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>pm</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>resources/img/gameObject/enemy/mob_2.png</t>
+          <t>resources/img/gameObject/enemy/mob_1.png</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Mob1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mob3</t>
+          <t>Mob2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q6</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>resources/img/gameObject/enemy/mob_3.png</t>
+          <t>resources/img/gameObject/enemy/mob_2.png</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Mob2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zombie</t>
+          <t>Mob3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sQ</t>
+          <t>q6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>resources/img/gameObject/enemy/zombie.png</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>bubble VFX</t>
+          <t>resources/img/gameObject/enemy/mob_3.png</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Mob3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Zombie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>qT</t>
+          <t>sQ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>resources/img/gameObject/soldier/soldier_3.png</t>
+          <t>resources/img/gameObject/enemy/zombie.png</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>yellow-circle VFX</t>
+          <t>bubble VFX</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
+          <t>Cavalry</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>qT</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>resources/img/gameObject/soldier/soldier_3.png</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yellow-circle VFX</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Puppet</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>oo</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>resources/img/gameObject/soldier/soldier_{skin}.png</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>1,1.2,1.4,1.6,1.8</t>
         </is>

--- a/Configs/GameConfig/Datas/enemy.xlsx
+++ b/Configs/GameConfig/Datas/enemy.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R19aa9d32af734598"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re20c1a3aad144ee7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -369,12 +369,14 @@
       <x:c r="A3" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3"/>
+      <x:c r="B3" t="str">
+        <x:v>主键，敌人唯一 ID</x:v>
+      </x:c>
       <x:c r="C3" t="str">
-        <x:v>类型索引</x:v>
+        <x:v>普通敌人类型索引，必须唯一；留空表示技能召唤类，不进入普通波次目录</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>资源地址</x:v>
+        <x:v>YooAsset Prefab 地址，如 Mob0，必须与 Prefab 文件名一致</x:v>
       </x:c>
       <x:c r="H3"/>
       <x:c r="I3"/>
@@ -397,12 +399,8 @@
       <x:c r="A5" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B5" t="str">
-        <x:v>ID(主键)</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>类型索引(与 ID 一致)</x:v>
-      </x:c>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
       <x:c r="D5"/>
       <x:c r="E5"/>
       <x:c r="F5"/>
